--- a/sheets/조재수대금교본/검수/상주 아리랑 (엇모리).xlsx
+++ b/sheets/조재수대금교본/검수/상주 아리랑 (엇모리).xlsx
@@ -3909,11 +3909,7 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -3921,11 +3917,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -3933,11 +3925,7 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21"/>
       <c r="O6" s="22"/>
@@ -3953,21 +3941,12 @@
         </is>
       </c>
       <c r="S6" s="22"/>
-      <c r="T6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T6" s="21"/>
       <c r="U6" s="22"/>
     </row>
     <row r="7" ht="127.68" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="B7" s="21"/>
       <c r="C7" s="22"/>
       <c r="D7" s="21"/>
       <c r="E7" s="22"/>
@@ -3975,31 +3954,15 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21"/>
       <c r="I7" s="22"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="J7" s="21"/>
       <c r="K7" s="22"/>
       <c r="L7" s="21"/>
       <c r="M7" s="22"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N7" s="21"/>
       <c r="O7" s="22"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P7" s="21"/>
       <c r="Q7" s="22"/>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="R7" s="21"/>
       <c r="S7" s="22"/>
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
@@ -4012,11 +3975,7 @@
         </is>
       </c>
       <c r="C8" s="22"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="22"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -4122,11 +4081,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="22"/>
       <c r="F10" s="21"/>
       <c r="G10" s="22"/>
@@ -4165,11 +4120,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="21"/>
       <c r="G11" s="22"/>
@@ -4181,42 +4132,22 @@
       <c r="I11" s="22"/>
       <c r="J11" s="21"/>
       <c r="K11" s="22"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L11" s="21"/>
       <c r="M11" s="22"/>
       <c r="N11" s="21"/>
       <c r="O11" s="22"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P11" s="21"/>
       <c r="Q11" s="22"/>
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
-      <c r="T11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
     <row r="12" ht="127.68" customHeight="true">
       <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
@@ -4224,17 +4155,9 @@
         </is>
       </c>
       <c r="G12" s="22"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H12" s="21"/>
       <c r="I12" s="22"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J12" s="21"/>
       <c r="K12" s="22"/>
       <c r="L12" s="21"/>
       <c r="M12" s="22"/>
@@ -4244,23 +4167,11 @@
         </is>
       </c>
       <c r="O12" s="22"/>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
-      <c r="R12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R12" s="21"/>
       <c r="S12" s="22"/>
-      <c r="T12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
     <row r="13" ht="6.0" customHeight="true">
@@ -4576,11 +4487,7 @@
         </is>
       </c>
       <c r="S24" s="22"/>
-      <c r="T24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T24" s="21"/>
       <c r="U24" s="22"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/상주 아리랑 (엇모리).xlsx
+++ b/sheets/조재수대금교본/검수/상주 아리랑 (엇모리).xlsx
@@ -3909,7 +3909,11 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -3917,7 +3921,11 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -3925,7 +3933,11 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21"/>
       <c r="O6" s="22"/>
@@ -3941,12 +3953,20 @@
         </is>
       </c>
       <c r="S6" s="22"/>
-      <c r="T6" s="21"/>
+      <c r="T6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U6" s="22"/>
     </row>
     <row r="7" ht="127.68" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C7" s="22"/>
       <c r="D7" s="21"/>
       <c r="E7" s="22"/>
@@ -3954,7 +3974,11 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21"/>
       <c r="I7" s="22"/>
-      <c r="J7" s="21"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K7" s="22"/>
       <c r="L7" s="21"/>
       <c r="M7" s="22"/>
@@ -3962,7 +3986,11 @@
       <c r="O7" s="22"/>
       <c r="P7" s="21"/>
       <c r="Q7" s="22"/>
-      <c r="R7" s="21"/>
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="S7" s="22"/>
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
@@ -3975,7 +4003,11 @@
         </is>
       </c>
       <c r="C8" s="22"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧</t>
+        </is>
+      </c>
       <c r="E8" s="22"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -4081,7 +4113,11 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E10" s="22"/>
       <c r="F10" s="21"/>
       <c r="G10" s="22"/>
@@ -4120,7 +4156,11 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E11" s="22"/>
       <c r="F11" s="21"/>
       <c r="G11" s="22"/>
@@ -4132,15 +4172,27 @@
       <c r="I11" s="22"/>
       <c r="J11" s="21"/>
       <c r="K11" s="22"/>
-      <c r="L11" s="21"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M11" s="22"/>
       <c r="N11" s="21"/>
       <c r="O11" s="22"/>
-      <c r="P11" s="21"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q11" s="22"/>
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
-      <c r="T11" s="21"/>
+      <c r="T11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="U11" s="22"/>
     </row>
     <row r="12" ht="127.68" customHeight="true">

--- a/sheets/조재수대금교본/검수/상주 아리랑 (엇모리).xlsx
+++ b/sheets/조재수대금교본/검수/상주 아리랑 (엇모리).xlsx
@@ -3664,32 +3664,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="127.68" customHeight="true">
+    <row r="3" ht="143.07" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="127.68" customHeight="true">
+    <row r="4" ht="143.07" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="127.68" customHeight="true">
+    <row r="5" ht="143.07" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="127.68" customHeight="true">
+    <row r="6" ht="143.07" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="127.68" customHeight="true">
+    <row r="7" ht="143.07" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="127.68" customHeight="true">
+    <row r="8" ht="143.07" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="127.68" customHeight="true">
+    <row r="9" ht="143.07" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="127.68" customHeight="true">
+    <row r="10" ht="143.07" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" ht="127.68" customHeight="true">
+    <row r="11" ht="143.07" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="127.68" customHeight="true">
+    <row r="12" ht="143.07" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4229,7 +4229,7 @@
     <row r="13" ht="6.0" customHeight="true">
       <c r="A13" s="0"/>
     </row>
-    <row r="14" ht="71.43" customHeight="true">
+    <row r="14" ht="80.0" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="20" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
       <c r="T14" s="20"/>
       <c r="U14" s="20"/>
     </row>
-    <row r="15" ht="127.68" customHeight="true">
+    <row r="15" ht="143.07" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="127.68" customHeight="true">
+    <row r="16" ht="143.07" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" ht="127.68" customHeight="true">
+    <row r="17" ht="143.07" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="127.68" customHeight="true">
+    <row r="18" ht="143.07" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="127.68" customHeight="true">
+    <row r="19" ht="143.07" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -4403,7 +4403,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="127.68" customHeight="true">
+    <row r="20" ht="143.07" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="127.68" customHeight="true">
+    <row r="21" ht="143.07" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="127.68" customHeight="true">
+    <row r="22" ht="143.07" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" ht="127.68" customHeight="true">
+    <row r="23" ht="143.07" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="127.68" customHeight="true">
+    <row r="24" ht="143.07" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
@@ -4549,7 +4549,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="12" max="16383" man="1"/>
   </rowBreaks>
